--- a/output/2026-09-07_15_Slovenia_Obalno-kraska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-07_15_Slovenia_Obalno-kraska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Attiva dal 1989, commercio all'ingrosso ferramenta/materiali metallici. Negozio online: viti/elementi di fissaggio, utensili, macchine, tecnologia di saldatura. Contatto verificato = pagina spletna trgovina (distinto dal centralino generale +386 5 662 60 30 / info@metaloprema.si).</t>
+          <t>Attiva dal 1989, commercio all'ingrosso ferramenta/materiali metallici. Negozio online: viti/elementi di fissaggio, utensili, macchine, tecnologia di saldatura. Contatto verificato = pagina spletna trgovina (distinto dal centralino generale +386 5 662 60 30 / info@metaloprema.si). [DUPLICATO — vedi anche: 2026-09-06_21_Slovenia_Osrednjeslovenska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Attiva dal 2008, SKD 46.620 commercio all'ingrosso di macchine utensili; oggetto sociale esplicito vendita attrezzature industriali per lavorazione metalli.</t>
+          <t>Attiva dal 2008, SKD 46.620 commercio all'ingrosso di macchine utensili; oggetto sociale esplicito vendita attrezzature industriali per lavorazione metalli. [DUPLICATO — vedi anche: 2026-09-07_06_Slovenia_Obalno-kraska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -600,7 +600,6 @@
           <t>GLOBAKE d.o.o. (trgovina s stroji)</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Sežana</t>
@@ -611,7 +610,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>office@globake.eu</t>

--- a/output/2026-09-07_15_Slovenia_Obalno-kraska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-07_15_Slovenia_Obalno-kraska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-07_15_Slovenia_Obalno-kraska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-07_15_Slovenia_Obalno-kraska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Filiale confermata; distributore tecnico multi-brand (cuscinetti, riduttori/motori, cinghie/pulegge, tenute, utensili) rilevante per manutenzione industriale/metalworking. Fonte: sito ufficiale e pagina contatti Tehimpex.</t>
+          <t>Filiale confermata; distributore tecnico multi-brand (cuscinetti, riduttori/motori, cinghie/pulegge, tenute, utensili) rilevante per manutenzione industriale/metalworking. Fonte: sito ufficiale e pagina contatti Tehimpex. [DUPLICATO — vedi anche: 2026-09-07_06_Slovenia_Obalno-kraska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
